--- a/Ultimate_Uniqorn_Leaderboard_Master.xlsx
+++ b/Ultimate_Uniqorn_Leaderboard_Master.xlsx
@@ -508,12 +508,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -523,12 +523,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stockton</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -538,12 +538,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Stockton</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -568,12 +568,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camby</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -583,12 +583,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lafayette</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lever</t>
+          <t>Camby</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -598,12 +598,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Lafayette</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Lever</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -643,12 +643,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Harden</t>
+          <t>Barkley</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -658,12 +658,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Barkley</t>
+          <t>Harden</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -718,12 +718,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wes</t>
+          <t>Larry</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unseld</t>
+          <t>Bird</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -748,12 +748,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Karl</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bird</t>
+          <t>Malone</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -763,12 +763,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karl</t>
+          <t>Wes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Malone</t>
+          <t>Unseld</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -793,12 +793,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Tree</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kidd</t>
+          <t>Rollins</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -808,12 +808,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Shaquille</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>O'Neal</t>
+          <t>Kidd</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -823,12 +823,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>Shaquille</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rollins</t>
+          <t>O'Neal</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -838,12 +838,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rivers</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -853,12 +853,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Steele</t>
+          <t>Iverson</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -868,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Alvan</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Iverson</t>
+          <t>Adams</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -883,12 +883,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Micheal</t>
+          <t>Alvin</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ray Richardson</t>
+          <t>Robertson</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -898,12 +898,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alvan</t>
+          <t>Micheal</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adams</t>
+          <t>Ray Richardson</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -913,12 +913,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alvin</t>
+          <t>Luka</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Robertson</t>
+          <t>Doncic</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -928,12 +928,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Luka</t>
+          <t>Larry</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Doncic</t>
+          <t>Steele</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -943,12 +943,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Rivers</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -958,12 +958,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1033,12 +1033,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Roundfield</t>
+          <t>McGinnis</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1048,12 +1048,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>McGinnis</t>
+          <t>Roundfield</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1108,12 +1108,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Outlaw</t>
+          <t>Lacey</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1123,12 +1123,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lacey</t>
+          <t>Outlaw</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1168,12 +1168,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Johnny</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1183,12 +1183,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Randy</t>
+          <t>Ralph</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Sampson</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1198,12 +1198,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Randy</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1228,12 +1228,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Scottie</t>
+          <t>Ennis</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pippen</t>
+          <t>Whatley</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1243,12 +1243,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Julius</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Erving</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1348,12 +1348,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Johnny</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1363,12 +1363,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ennis</t>
+          <t>Julius</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Whatley</t>
+          <t>Erving</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1393,12 +1393,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ralph</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sampson</t>
+          <t>Ewing</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1408,12 +1408,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Otis</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McHale</t>
+          <t>Birdsong</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1423,12 +1423,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ewing</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1438,12 +1438,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Otis</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Birdsong</t>
+          <t>McHale</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1468,12 +1468,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Thurmond</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Thurmond</t>
+          <t>Archibald</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1513,12 +1513,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Archibald</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1528,12 +1528,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LeBron</t>
+          <t>Moses</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Malone</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1543,12 +1543,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>LeBron</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1573,12 +1573,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Moses</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Malone</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1588,12 +1588,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Embiid</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1603,12 +1603,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Elvin</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Embiid</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1618,12 +1618,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Dikembe</t>
+          <t>Dwight</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mutombo</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1633,12 +1633,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Eddie</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1648,12 +1648,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Dwight</t>
+          <t>Damian</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Lillard</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1663,12 +1663,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Baron</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Manning</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1678,12 +1678,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1693,12 +1693,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Darrell</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1708,12 +1708,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Darrell</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1723,12 +1723,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Deron</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Manning</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1738,12 +1738,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Dominique</t>
+          <t>Benoit</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wilkins</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1753,12 +1753,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Dirk</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Nowitzki</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1768,12 +1768,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Damian</t>
+          <t>Baron</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lillard</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1783,12 +1783,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Artis</t>
+          <t>Dominique</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Gilmore</t>
+          <t>Wilkins</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1798,12 +1798,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Artis</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Drummond</t>
+          <t>Gilmore</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1813,12 +1813,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dirk</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nowitzki</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1828,12 +1828,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Deron</t>
+          <t>Dikembe</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Mutombo</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1858,12 +1858,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Elvin</t>
+          <t>Alonzo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Mourning</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1873,12 +1873,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Benoit</t>
+          <t>Eddie</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1888,12 +1888,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Alonzo</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mourning</t>
+          <t>Drummond</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1903,27 +1903,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Bobby</t>
+          <t>Antawn</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Jamison</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Westphal</t>
+          <t>Batum</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pressey</t>
+          <t>Westphal</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1948,12 +1948,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Buckner</t>
+          <t>Pressey</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2008,12 +2008,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Otto</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dandridge</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2023,12 +2023,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Brook</t>
+          <t>Trae</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lopez</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2038,12 +2038,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Otto</t>
+          <t>Boris</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Diaw</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2053,12 +2053,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Boris</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Diaw</t>
+          <t>Roy</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2068,12 +2068,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Andray</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Roy</t>
+          <t>Blatche</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2083,12 +2083,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Billy</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2098,12 +2098,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Batum</t>
+          <t>Haliburton</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2113,12 +2113,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Dandridge</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2128,12 +2128,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Brook</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Lopez</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2143,12 +2143,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Oakley</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2158,12 +2158,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Tyrone</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Corbin</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2173,12 +2173,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Moussa</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Diabate</t>
+          <t>Oakley</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2188,12 +2188,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Moussa</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Diabate</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2203,12 +2203,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mullin</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2218,12 +2218,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Monta</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ellis</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2233,12 +2233,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Monta</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Woodson</t>
+          <t>Ellis</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Gale</t>
+          <t>Woodson</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2263,12 +2263,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ramon</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sessions</t>
+          <t>Gale</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2278,12 +2278,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bledsoe</t>
+          <t>Mullin</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2293,12 +2293,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Rich</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kelley</t>
+          <t>Buckner</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2308,12 +2308,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sherman</t>
+          <t>Billy</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2323,12 +2323,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tyrone</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Corbin</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2338,12 +2338,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Ramon</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Haliburton</t>
+          <t>Sessions</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2353,12 +2353,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Andray</t>
+          <t>Sidney</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Blatche</t>
+          <t>Lowe</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2368,12 +2368,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Trae</t>
+          <t>Sherman</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Douglas</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2383,12 +2383,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Shawn</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Boerwinkle</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2398,12 +2398,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Carr</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2413,12 +2413,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Terry</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Stipanovich</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2428,12 +2428,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Terrell</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2443,12 +2443,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2458,12 +2458,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Scottie</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Stipanovich</t>
+          <t>Pippen</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2473,12 +2473,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Antawn</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Jamison</t>
+          <t>Skiles</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2488,12 +2488,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>McDyess</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2503,12 +2503,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sidney</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Lowe</t>
+          <t>Bowie</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2518,12 +2518,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Shawn</t>
+          <t>Terrell</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2533,12 +2533,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rudy</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Covington</t>
+          <t>Gobert</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2548,12 +2548,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Ronny</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Carr</t>
+          <t>Turiaf</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2563,12 +2563,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Gilgeous-Alexander</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2578,12 +2578,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Terry</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>McDyess</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2593,12 +2593,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Skiles</t>
+          <t>Williams III</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2608,12 +2608,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Bowie</t>
+          <t>Parish</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2623,12 +2623,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Rudy</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Gobert</t>
+          <t>Cooper</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2638,12 +2638,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Ronny</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Turiaf</t>
+          <t>Pack</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2653,12 +2653,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Covington</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2683,12 +2683,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rich</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Williams III</t>
+          <t>Kelley</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2698,12 +2698,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Clifford</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2713,12 +2713,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Parish</t>
+          <t>Boerwinkle</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2728,12 +2728,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Clifford</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Pack</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2743,12 +2743,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Clifford</t>
+          <t>Marc</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Gasol</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2758,12 +2758,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Metta</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Porter Jr.</t>
+          <t>World Peace</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2773,12 +2773,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Clifford</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Cooper</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2788,12 +2788,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Eddie</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2818,12 +2818,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2833,12 +2833,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Joe</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2848,12 +2848,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Joakim</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2863,12 +2863,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Joakim</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2878,12 +2878,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>McElroy</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -2908,12 +2908,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Jerry</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>McElroy</t>
+          <t>Stackhouse</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -2923,12 +2923,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Jerry</t>
+          <t>Jerome</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Stackhouse</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2938,12 +2938,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Jerome</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -2953,12 +2953,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -2983,12 +2983,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Jamal</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -2998,12 +2998,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Jamaal</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Tinsley</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3013,12 +3013,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Wetzel</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3028,12 +3028,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Jamaal</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tinsley</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3043,12 +3043,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Rod Williams</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3058,12 +3058,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Hersey</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Hawkins</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3073,12 +3073,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Eddie</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Rod Williams</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3088,12 +3088,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Hersey</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Hawkins</t>
+          <t>Stiemsma</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3103,12 +3103,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Elfrid</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Payton</t>
+          <t>Ostertag</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3118,12 +3118,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Elfrid</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Stiemsma</t>
+          <t>Payton</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3133,12 +3133,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Elliot</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ostertag</t>
+          <t>Perry</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3148,12 +3148,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Elliot</t>
+          <t>Elton</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Perry</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3163,12 +3163,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Elton</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Gervin</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3178,12 +3178,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Garfield</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Gervin</t>
+          <t>Heard</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3193,12 +3193,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Garfield</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Heard</t>
+          <t>VanVleet</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3208,12 +3208,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>VanVleet</t>
+          <t>Snow</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3238,12 +3238,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Jrue</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>Wetzel</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3253,12 +3253,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Metta</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>World Peace</t>
+          <t>Booker</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3268,12 +3268,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Darnell</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Kenon</t>
+          <t>Hillman</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3283,12 +3283,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Corey</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Brewer</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3298,12 +3298,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Mario</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Chalmers</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3313,12 +3313,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Mario</t>
+          <t>Corey</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Chalmers</t>
+          <t>Brewer</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Snow</t>
+          <t>Bledsoe</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3343,12 +3343,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Marc</t>
+          <t>Manute</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Gasol</t>
+          <t>Bol</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3358,12 +3358,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Manute</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Bol</t>
+          <t>Porter Jr.</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3403,12 +3403,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Lionel</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Issel</t>
+          <t>Simmons</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Simmons</t>
+          <t>Hollins</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3433,12 +3433,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Lionel</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Hollins</t>
+          <t>Issel</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3463,12 +3463,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Darnell</t>
+          <t>Larry</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Hillman</t>
+          <t>Kenon</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3478,12 +3478,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Darnell</t>
+          <t>Lamar</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Odom</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3493,12 +3493,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Jrue</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Dixon</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3508,12 +3508,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Lamar</t>
+          <t>Darnell</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Odom</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3688,12 +3688,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Booker</t>
+          <t>Dixon</t>
         </is>
       </c>
       <c r="C218" t="n">
